--- a/extenbooks/XS2301_extenbook.xlsx
+++ b/extenbooks/XS2301_extenbook.xlsx
@@ -967,19 +967,19 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B33" t="n">
-        <v>-468.262</v>
+        <v>-124.068</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>XS2301-world</t>
+          <t>XS2301-china</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C0004</t>
+          <t>CENSUS_FT900_C5700</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -990,10 +990,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B34" t="n">
-        <v>-124.068</v>
+        <v>-162.254</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1013,19 +1013,19 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="B35" t="n">
-        <v>-532.35</v>
+        <v>-202.278</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>XS2301-world</t>
+          <t>XS2301-china</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C0004</t>
+          <t>CENSUS_FT900_C5700</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1036,10 +1036,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="B36" t="n">
-        <v>-162.254</v>
+        <v>-234.101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1059,19 +1059,19 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="B37" t="n">
-        <v>-654.828</v>
+        <v>-258.506</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>XS2301-world</t>
+          <t>XS2301-china</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C0004</t>
+          <t>CENSUS_FT900_C5700</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1082,10 +1082,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="B38" t="n">
-        <v>-202.278</v>
+        <v>-268.04</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1105,19 +1105,19 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2005</v>
+        <v>2009</v>
       </c>
       <c r="B39" t="n">
-        <v>-772.374</v>
+        <v>-226.877</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>XS2301-world</t>
+          <t>XS2301-china</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C0004</t>
+          <t>CENSUS_FT900_C5700</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2006</v>
+        <v>2010</v>
       </c>
       <c r="B40" t="n">
-        <v>-234.101</v>
+        <v>-273.042</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1151,19 +1151,19 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2006</v>
+        <v>2011</v>
       </c>
       <c r="B41" t="n">
-        <v>-827.97</v>
+        <v>-295.25</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>XS2301-world</t>
+          <t>XS2301-china</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C0004</t>
+          <t>CENSUS_FT900_C5700</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1174,10 +1174,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2007</v>
+        <v>2012</v>
       </c>
       <c r="B42" t="n">
-        <v>-258.506</v>
+        <v>-315.103</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1197,19 +1197,19 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2007</v>
+        <v>2013</v>
       </c>
       <c r="B43" t="n">
-        <v>-808.765</v>
+        <v>-318.684</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>XS2301-world</t>
+          <t>XS2301-china</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C0004</t>
+          <t>CENSUS_FT900_C5700</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1220,10 +1220,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2008</v>
+        <v>2014</v>
       </c>
       <c r="B44" t="n">
-        <v>-268.04</v>
+        <v>-344.818</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1243,19 +1243,19 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2008</v>
+        <v>2015</v>
       </c>
       <c r="B45" t="n">
-        <v>-816.2</v>
+        <v>-367.328</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>XS2301-world</t>
+          <t>XS2301-china</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C0004</t>
+          <t>CENSUS_FT900_C5700</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -1266,10 +1266,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2009</v>
+        <v>2016</v>
       </c>
       <c r="B46" t="n">
-        <v>-226.877</v>
+        <v>-346.825</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1289,19 +1289,19 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2009</v>
+        <v>2017</v>
       </c>
       <c r="B47" t="n">
-        <v>-503.583</v>
+        <v>-375.168</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>XS2301-world</t>
+          <t>XS2301-china</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C0004</t>
+          <t>CENSUS_FT900_C5700</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -1312,10 +1312,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2010</v>
+        <v>2018</v>
       </c>
       <c r="B48" t="n">
-        <v>-273.042</v>
+        <v>-418.233</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1335,19 +1335,19 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2010</v>
+        <v>2019</v>
       </c>
       <c r="B49" t="n">
-        <v>-635.365</v>
+        <v>-342.63</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>XS2301-world</t>
+          <t>XS2301-china</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C0004</t>
+          <t>CENSUS_FT900_C5700</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -1358,10 +1358,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2011</v>
+        <v>2020</v>
       </c>
       <c r="B50" t="n">
-        <v>-295.25</v>
+        <v>-307.966</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1381,19 +1381,19 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2011</v>
+        <v>2021</v>
       </c>
       <c r="B51" t="n">
-        <v>-725.447</v>
+        <v>-352.807</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>XS2301-world</t>
+          <t>XS2301-china</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C0004</t>
+          <t>CENSUS_FT900_C5700</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -1404,10 +1404,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2012</v>
+        <v>2022</v>
       </c>
       <c r="B52" t="n">
-        <v>-315.103</v>
+        <v>-382.281</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1427,19 +1427,19 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2012</v>
+        <v>2023</v>
       </c>
       <c r="B53" t="n">
-        <v>-730.446</v>
+        <v>-279.608</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>XS2301-world</t>
+          <t>XS2301-china</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C0004</t>
+          <t>CENSUS_FT900_C5700</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -1450,10 +1450,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="B54" t="n">
-        <v>-318.684</v>
+        <v>-297.048</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1473,10 +1473,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2013</v>
+        <v>2002</v>
       </c>
       <c r="B55" t="n">
-        <v>-689.47</v>
+        <v>-468.262</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -1496,19 +1496,19 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2014</v>
+        <v>2003</v>
       </c>
       <c r="B56" t="n">
-        <v>-344.818</v>
+        <v>-532.35</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>XS2301-china</t>
+          <t>XS2301-world</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C5700</t>
+          <t>CENSUS_FT900_C0004</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1519,10 +1519,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2014</v>
+        <v>2004</v>
       </c>
       <c r="B57" t="n">
-        <v>-734.482</v>
+        <v>-654.828</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1542,19 +1542,19 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2015</v>
+        <v>2005</v>
       </c>
       <c r="B58" t="n">
-        <v>-367.328</v>
+        <v>-772.374</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>XS2301-china</t>
+          <t>XS2301-world</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C5700</t>
+          <t>CENSUS_FT900_C0004</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -1565,10 +1565,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2015</v>
+        <v>2006</v>
       </c>
       <c r="B59" t="n">
-        <v>-745.4829999999999</v>
+        <v>-827.97</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -1588,19 +1588,19 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2016</v>
+        <v>2007</v>
       </c>
       <c r="B60" t="n">
-        <v>-346.825</v>
+        <v>-808.765</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>XS2301-china</t>
+          <t>XS2301-world</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C5700</t>
+          <t>CENSUS_FT900_C0004</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -1611,10 +1611,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="B61" t="n">
-        <v>-735.326</v>
+        <v>-816.2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -1634,19 +1634,19 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="B62" t="n">
-        <v>-375.168</v>
+        <v>-503.583</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>XS2301-china</t>
+          <t>XS2301-world</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C5700</t>
+          <t>CENSUS_FT900_C0004</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -1657,10 +1657,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2017</v>
+        <v>2010</v>
       </c>
       <c r="B63" t="n">
-        <v>-792.396</v>
+        <v>-635.365</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -1680,19 +1680,19 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2018</v>
+        <v>2011</v>
       </c>
       <c r="B64" t="n">
-        <v>-418.233</v>
+        <v>-725.447</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>XS2301-china</t>
+          <t>XS2301-world</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C5700</t>
+          <t>CENSUS_FT900_C0004</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2018</v>
+        <v>2012</v>
       </c>
       <c r="B65" t="n">
-        <v>-870.3579999999999</v>
+        <v>-730.446</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1726,19 +1726,19 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2019</v>
+        <v>2013</v>
       </c>
       <c r="B66" t="n">
-        <v>-342.63</v>
+        <v>-689.47</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>XS2301-china</t>
+          <t>XS2301-world</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C5700</t>
+          <t>CENSUS_FT900_C0004</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -1749,10 +1749,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="B67" t="n">
-        <v>-845.759</v>
+        <v>-734.482</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1772,19 +1772,19 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="B68" t="n">
-        <v>-307.966</v>
+        <v>-745.4829999999999</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>XS2301-china</t>
+          <t>XS2301-world</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C5700</t>
+          <t>CENSUS_FT900_C0004</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="B69" t="n">
-        <v>-901.482</v>
+        <v>-735.326</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1818,19 +1818,19 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2021</v>
+        <v>2017</v>
       </c>
       <c r="B70" t="n">
-        <v>-352.807</v>
+        <v>-792.396</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>XS2301-china</t>
+          <t>XS2301-world</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C5700</t>
+          <t>CENSUS_FT900_C0004</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -1841,10 +1841,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2021</v>
+        <v>2018</v>
       </c>
       <c r="B71" t="n">
-        <v>-1070.772</v>
+        <v>-870.3579999999999</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1864,19 +1864,19 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="B72" t="n">
-        <v>-382.281</v>
+        <v>-845.759</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>XS2301-china</t>
+          <t>XS2301-world</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C5700</t>
+          <t>CENSUS_FT900_C0004</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -1887,10 +1887,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B73" t="n">
-        <v>-1167.085</v>
+        <v>-901.482</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1910,19 +1910,19 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B74" t="n">
-        <v>-279.608</v>
+        <v>-1070.772</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>XS2301-china</t>
+          <t>XS2301-world</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C5700</t>
+          <t>CENSUS_FT900_C0004</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -1933,10 +1933,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="B75" t="n">
-        <v>-1054.613</v>
+        <v>-1167.085</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1956,19 +1956,19 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B76" t="n">
-        <v>-297.048</v>
+        <v>-1054.613</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>XS2301-china</t>
+          <t>XS2301-world</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_C5700</t>
+          <t>CENSUS_FT900_C0004</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2012,7 +2012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A198"/>
+  <dimension ref="A1:A191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2051,42 +2051,38 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>**Phase**: 5 (Ingestion)</t>
+          <t>**Series ID**: XS2301</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>**Series ID**: XS2301 (rescoped per decision 0006)</t>
+          <t>**Status**: study_complete</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: study_complete</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t>**Revised**: 2026-06-11 (truncation repair: loader rebuilt on the Census country pages; coverage now genuinely continuous 2002–2024)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>**Author**: opus-fanout-ES</t>
-        </is>
-      </c>
+      <c r="A11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>**Revised**: 2026-06-11 (XS reconciliation — truncation repair: loader rebuilt on Census country pages; coverage now genuinely continuous 2002–2024)</t>
+          <t>## 1. Definition</t>
         </is>
       </c>
     </row>
@@ -2096,244 +2092,244 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>## 1. Definition</t>
+          <t>XS2301 is the annual US merchandise (goods) trade balance against **two**</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>trading partners: (i) World Total; (ii) China. Both in Billion current USD,</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>XS2301 is the annual US merchandise (goods) trade balance against **two**</t>
+          <t>Census basis (Total Exports Value − Customs Import Value). Paper source:</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>trading partners: (i) World Total; (ii) China. Both in Billion current USD,</t>
+          <t>Weber &amp; Shaikh (2020), Appendix Figure 1 (p. 453), which plots 2002–2017.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Census basis (Total Exports Value − Customs Import Value). Paper source:</t>
+          <t>We extend the same source forward to 2024.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Weber &amp; Shaikh (2020), Appendix Figure 1 (p. 453), which plots 2002–2017.</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>We extend the same source forward to 2024.</t>
+          <t>Per US Census FT900 convention (FT900 is the Census Bureau's monthly</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>foreign-trade statistics report), both series are negative throughout the window</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Per Census FT900 convention, both series are negative throughout the window</t>
+          <t>(the US runs a goods-trade deficit). The constructed Census series reproduces</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>(the US runs a goods-trade deficit). The constructed Census series reproduces</t>
+          <t>the paper's Figure 1 endpoints to within figure-read precision: World Total</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>the paper's Figure 1 endpoints to within figure-read precision: World Total</t>
+          <t>2002 = -468.3 bn (paper figure-read ≈ -474), 2017 = -792.4 bn (≈ -810);</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2002 = -468.3 bn (paper figure-read ≈ -474), 2017 = -792.4 bn (≈ -810);</t>
+          <t>China 2002 = -103.1 bn (≈ -103), 2017 = -375.2 bn (≈ -376).</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>China 2002 = -103.1 bn (≈ -103), 2017 = -375.2 bn (≈ -376).</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>## 2. Why it matters</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>## 2. Why it matters</t>
-        </is>
-      </c>
+      <c r="A28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Figure 1 is the paper's headline: the bilateral US-China deficit grew from</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Figure 1 is the paper's headline: the bilateral US-China deficit grew from</t>
+          <t>"around one-fifth" of the total US deficit in 2002 to "about one-third" by</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>"around one-fifth" of the total US deficit in 2002 to "about one-third" by</t>
+          <t>2008 (paper p. 432). Decomposing the world-total deficit into the China share</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2008 (paper p. 432). Decomposing the world-total deficit into the China share</t>
+          <t>is the empirical hook for the paper's currency-manipulation critique.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>is the empirical hook for the paper's currency-manipulation critique.</t>
-        </is>
-      </c>
+      <c r="A33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>## 3. Sources</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>## 3. Sources</t>
-        </is>
-      </c>
+      <c r="A35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>| Subseries | Coverage | Source | Native units | Retrieval |</t>
+          <t>|---|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>|---|---|---|---|---|</t>
+          <t>| XS2301-world | 2002–2024 | US Census FT900, All-countries goods balance page (c0004) | Millions USD | `census.gov/foreign-trade/balance/c0004.html` |</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>| XS2301-world | 2002–2024 | US Census FT900, All-countries goods balance page (c0004) | Millions USD | `census.gov/foreign-trade/balance/c0004.html` |</t>
+          <t>| XS2301-china | 2002–2024 | US Census FT900, China goods balance page (c5700) | Millions USD | `census.gov/foreign-trade/balance/c5700.html` |</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>| XS2301-china | 2002–2024 | US Census FT900, China goods balance page (c5700) | Millions USD | `census.gov/foreign-trade/balance/c5700.html` |</t>
-        </is>
-      </c>
+      <c r="A40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Both pages are public, key-free HTML and carry one `TOTAL {YYYY}` annual row</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Both pages are public, key-free HTML and carry one `TOTAL {YYYY}` annual row</t>
+          <t>per year-table (Exports / Imports / Balance, current USD millions, Census</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>per year-table (Exports / Imports / Balance, current USD millions, Census</t>
+          <t>basis). This is the same source family the paper used for Figure 1.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>basis). This is the same source family the paper used for Figure 1.</t>
-        </is>
-      </c>
+      <c r="A44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>## 4. Construction</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>## 4. Construction</t>
-        </is>
-      </c>
+      <c r="A46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>For each partner, read the `TOTAL {YYYY}` annual rows from the Census country</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>For each partner, read the `TOTAL {YYYY}` annual rows from the Census country</t>
+          <t>page; take the published annual Balance (millions USD), and divide by 1000 to</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>page; take the published annual Balance (millions USD), and divide by 1000 to</t>
+          <t>present in Billion USD. The two partners are emitted as two subseries —</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>present in Billion USD. The loader emits the two partner series as two</t>
+          <t>`XS2301-world` and `XS2301-china` (the suffix after the series id names the</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>subseries (XS2301-world, XS2301-china) with the partner labeled in</t>
+          <t>trading partner) — with each observation labelled by its partner and year.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>`country_key`; the chopped writer disambiguates uniqueness on</t>
-        </is>
-      </c>
+      <c r="A52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>`(year, subseries_id, country_key)`.</t>
+          <t>## 5. Year coverage</t>
         </is>
       </c>
     </row>
@@ -2343,52 +2339,52 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>## 5. Year coverage</t>
+          <t>- Paper window (plotted in Fig 1): 2002–2017 (16 obs per partner)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>- Continued from the same source: 2018–2024 (7 obs; Section 301 tariffs in</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>- Paper window (plotted in Fig 1): 2002–2017 (16 obs per partner)</t>
+          <t xml:space="preserve">  2018-19 and COVID in 2020 create structural shifts — interpretive, not data</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>- Continued from the same source: 2018–2024 (7 obs; Section 301 tariffs in</t>
+          <t xml:space="preserve">  gaps)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2018-19 and COVID in 2020 create structural shifts — interpretive, not data</t>
+          <t>- **Total: 2002–2024 — 23 obs per partner, 46 rows long form, genuinely</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">  gaps)</t>
+          <t xml:space="preserve">  continuous (no missing years).**</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>- **Total: 2002–2024 — 23 obs per partner, 46 rows long form, genuinely</t>
-        </is>
-      </c>
+      <c r="A61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">  continuous (no missing years).**</t>
+          <t>## 6. Units</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2394,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>## 6. Units</t>
+          <t>`billion_usd` (loader divides the Census millions figure by 1000).</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2404,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>`billion_usd` (loader divides the Census millions figure by 1000).</t>
+          <t>## 7. Caveats</t>
         </is>
       </c>
     </row>
@@ -2418,269 +2414,258 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>## 7. Caveats</t>
+          <t>1. Census-basis (Total Exports Value − Customs Import Value) differs slightly</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   from BoP-basis (balance-of-payments basis, US Bureau of Economic Analysis</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1. Census-basis (Total Exports Value − Customs Import Value) differs slightly</t>
+          <t xml:space="preserve">   (BEA) International Transactions); the paper uses Census</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">   from BoP-basis (BEA International Transactions); the paper uses Census</t>
+          <t xml:space="preserve">   basis per the Fig 1 footnote, which is what these pages publish.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">   basis per the Fig 1 footnote, which is what these pages publish.</t>
+          <t>2. Section 301 tariffs (2018-) and COVID (2020) create structural breaks in</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2. Section 301 tariffs (2018-) and COVID (2020) create structural breaks in</t>
+          <t xml:space="preserve">   the post-paper years — interpretive, not data gaps.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">   the post-paper years — interpretive, not data gaps.</t>
+          <t>3. The world-total figure-read endpoints in the paper (-474 in 2002, -810 in</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3. The world-total figure-read endpoints in the paper (-474 in 2002, -810 in</t>
+          <t xml:space="preserve">   2017) are eyeballed off the appendix chart; the constructed Census source</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">   2017) are eyeballed off the appendix chart; the constructed Census source</t>
+          <t xml:space="preserve">   values (-468.3, -792.4) differ by 1.2–2.2%, well within the ±10% validator</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">   values (-468.3, -792.4) differ by 1.2–2.2%, well within the ±10% validator</t>
+          <t xml:space="preserve">   tolerance. The China endpoints match the paper to &lt;1%.</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   tolerance. The China endpoints match the paper to &lt;1%.</t>
-        </is>
-      </c>
+      <c r="A78" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr"/>
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>## 8. Revision history — truncation repair (2026-06-11)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>## 8. Revision history — truncation repair (2026-06-11)</t>
-        </is>
-      </c>
+      <c r="A80" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>The earlier loader attempted a fragile Census scrape that keyed annual figures</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>The earlier loader attempted a fragile Census scrape that keyed annual figures</t>
+          <t>off a four-digit *column header* that does not exist on the country pages (the</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>off a four-digit *column header* that does not exist on the country pages (the</t>
+          <t>year lives in the `TOTAL {YYYY}` Month cell). The scrape therefore always</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>year lives in the `TOTAL {YYYY}` Month cell). The scrape therefore always</t>
+          <t>failed and the series silently degraded to the five salvaged Fig-1 *anchor*</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>failed and the series silently degraded to the five salvaged Fig-1 *anchor*</t>
+          <t>points (World 2002/2017; China 2002/2017/2018), which truncated the series at</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>points (World 2002/2017; China 2002/2017/2018), which truncated the series at</t>
+          <t>2018 and were figure-reads rather than source data — while the DPR claimed</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2018 and were figure-reads rather than source data — while the DPR claimed</t>
+          <t>continuous coverage to 2024.</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>continuous coverage to 2024.</t>
-        </is>
-      </c>
+      <c r="A88" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>The loader was rebuilt to read the `TOTAL {YYYY}` rows directly from the</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>The loader was rebuilt (`L01_XS2301.py` + new `S00_apis.census_country_annual_balance`)</t>
+          <t>Census World (c0004) and China (c5700) country pages. Result: 23 real annual</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>to read the `TOTAL {YYYY}` rows directly from the Census c0004 (World) and</t>
+          <t>observations per partner, 2002–2024, no fabrication, no interpolation.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>c5700 (China) pages. Result: 23 real annual observations per partner,</t>
+          <t>Validation PASS (4/4 anchors matched, max 2.17% error). The verbatim Figure 1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2002–2024, no fabrication, no interpolation. Validator V03_XS2301 PASS</t>
+          <t>anchors are retained only as a per-partner last-resort fallback if a page</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>(4/4 anchors matched, max 2.17% error). The verbatim Fig 1 anchors are</t>
+          <t>fetch fails.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>retained only as a per-partner last-resort fallback if a page fetch fails.</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>## 9. Cross-references</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>&gt; Source-id note: the World subseries now draws on the all-countries balance</t>
-        </is>
-      </c>
+      <c r="A97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>&gt; page (c0004); the registry currently records `CENSUS_FT900_EXH1` /</t>
+          <t>- Related: XS2302, XS2303, XS2304, XS2305 (other Weber-Shaikh figures);</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>&gt; `exh1.txt` (a historical path that now 404s). Recommended registry</t>
+          <t xml:space="preserve">  S1101 (Ch11 trade balance, different concept)</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>&gt; reconciliation: rename the World subsource to `CENSUS_FT900_C0004` with</t>
-        </is>
-      </c>
+      <c r="A100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>&gt; `source_url = census.gov/foreign-trade/balance/c0004.html`. Flagged in the</t>
+          <t>## 10. Validation expectation</t>
         </is>
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>&gt; triage patch (registry is read-only in this pass).</t>
-        </is>
-      </c>
+      <c r="A102" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>- Tolerance: ±10% (figure-read precision on the World endpoints; Census</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>## 9. Cross-references</t>
+          <t xml:space="preserve">  periodic revisions can shift historical totals 1–3%).</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>- Anchors from Fig 1: world-total 2002 ≈ -474 bn, 2017 ≈ -810 bn;</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>- Dossier: `XS2301_research.json` (decision 0006 rescoped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>- Related: XS2302, XS2303, XS2304, XS2305 (other Weber-Shaikh figures);</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  S1101 (Ch11 trade balance, different concept)</t>
+          <t xml:space="preserve">  china 2002 ≈ -103 bn, 2017 ≈ -376 bn. All satisfied (see §1).</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" s="4">
+        <f>== EPR: XS2301_EPR.md ===</f>
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>## 10. Validation expectation</t>
+          <t># XS2301 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -2690,106 +2675,113 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>- Tolerance: ±10% (figure-read precision on the World endpoints; Census</t>
+          <t>**Series**: XS2301 — US Trade Balance (World, China)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">  periodic revisions can shift historical totals 1–3%).</t>
+          <t>**Construction**: `direct` (two parallel partner pulls)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>- Anchors from Fig 1: world-total 2002 ≈ -474 bn, 2017 ≈ -810 bn;</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  china 2002 ≈ -103 bn, 2017 ≈ -376 bn. All satisfied (see §1).</t>
-        </is>
-      </c>
+      <c r="A115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>## 1. Extendability</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="4">
-        <f>== EPR: XS2301_EPR.md ===</f>
-        <v/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>US Census FT900 (the Census Bureau's monthly foreign-trade statistics report)</t>
+        </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t># XS2301 — Extension Provenance Record</t>
+          <t>is continuously published monthly. Per-country totals for</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>China extend back to 1985 and forward to current. Extension to 2024 is</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>**Series**: XS2301 — US Trade Balance (World, China)</t>
+          <t>mechanical with the caveat that:</t>
         </is>
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
+      <c r="A122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>**Construction**: `direct` (two parallel partner pulls)</t>
+          <t>- 2018-2019 Section 301 tariffs introduce a documented structural break</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>**Authored**: 2026-05-18</t>
+          <t xml:space="preserve">  in import-value composition (tariff-inclusive vs not).</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>- 2020 COVID compresses bilateral trade flows.</t>
+        </is>
+      </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>## 1. Extendability</t>
-        </is>
-      </c>
+      <c r="A126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Neither caveat blocks extension — both are documented in the extension</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Census FT900 is continuously published monthly. Per-country totals for</t>
+          <t>narrative.</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>China extend back to 1985 and forward to current. Extension to 2024 is</t>
-        </is>
-      </c>
+      <c r="A129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>mechanical with the caveat that:</t>
+          <t>## 2. Method</t>
         </is>
       </c>
     </row>
@@ -2799,138 +2791,130 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>- 2018-2019 Section 301 tariffs introduce a documented structural break</t>
+          <t>For each partner (world = Census page c0004, china = Census page c5700):</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">  in import-value composition (tariff-inclusive vs not).</t>
+          <t>1. The loader pulls the Census country balance page (rebuilt 2026-06-11 to</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>- 2020 COVID compresses bilateral trade flows.</t>
+          <t xml:space="preserve">   replace a prior fragile scrape that mis-keyed the year off a non-existent</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   column header and silently truncated the series at 2018).</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Neither caveat blocks extension — both are documented in the paper-Phase</t>
+          <t>2. Reads the published `TOTAL {YYYY}` annual Balance row directly (Census</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>6 extension narrative.</t>
+          <t xml:space="preserve">   already aggregates the months); no month summing required.</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>3. Converts to Billion USD (divide millions by 1000).</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>## 2. Method</t>
+          <t>4. Emits two subseries, `XS2301-world` and `XS2301-china` (the suffix names</t>
         </is>
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   the trading partner).</t>
+        </is>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>For each partner (world=c0004, china=c5700):</t>
-        </is>
-      </c>
+      <c r="A141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1. Loader pulls the Census country balance page via</t>
+          <t>Result: genuinely continuous 2002–2024, 23 obs/partner, all live Census data;</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">   `census_country_annual_balance` (rebuilt 2026-06-11; replaces the prior</t>
+          <t>validation PASS (4/4 Figure 1 anchors, max 2.17% error).</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   fragile `census_ft900_annual_balance` scrape that mis-keyed the year off a</t>
-        </is>
-      </c>
+      <c r="A144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">   non-existent column header and silently truncated the series at 2018).</t>
+          <t>## 3. Proxies</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>2. Reads the published `TOTAL {YYYY}` annual Balance row directly (Census</t>
-        </is>
-      </c>
+      <c r="A146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">   already aggregates the months); no month summing required.</t>
+          <t>None. Census FT900 IS the source the paper cites.</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>3. Converts to Billion USD (divide millions by 1000).</t>
-        </is>
-      </c>
+      <c r="A148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>4. Emits as `subseries_id={XS2301-world | XS2301-china}` with</t>
+          <t>## 4. Synthetic data</t>
         </is>
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   `country_key={World|China}`.</t>
-        </is>
-      </c>
+      <c r="A150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>None. NaN propagates.</t>
+        </is>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Result: genuinely continuous 2002–2024, 23 obs/partner, all live Census data;</t>
-        </is>
-      </c>
+      <c r="A152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>V03 validator PASS (4/4 Fig 1 anchors, max 2.17% error).</t>
+          <t>## 5. Failure modes</t>
         </is>
       </c>
     </row>
@@ -2940,266 +2924,237 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>## 3. Proxies</t>
+          <t>- Census HTML layout change: loader returns degraded; processor</t>
         </is>
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  publishes whichever partner parsed.</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>None. Census FT900 IS the source the paper cites.</t>
+          <t>- USA Trade Online auth-required path: not used; we stick to the</t>
         </is>
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  public HTML/text pages.</t>
+        </is>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>## 4. Synthetic data</t>
-        </is>
-      </c>
+      <c r="A159" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>## 6. Conceptual continuity vs adjacent concepts</t>
+        </is>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>None. NaN propagates.</t>
-        </is>
-      </c>
+      <c r="A161" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>The extension proxy `Census FT900 Exhibit 1 (world) + c5700 (China)` measures</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>## 5. Failure modes</t>
+          <t>`US merchandise (goods) trade balance, Census basis` rather than</t>
         </is>
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>`US current account` or `BoP-basis goods balance` (balance-of-payments basis)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>- Census HTML layout change: loader returns degraded; processor</t>
+          <t>because:</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t xml:space="preserve">  publishes whichever partner parsed.</t>
+          <t>- Source agency choice: Weber &amp; Shaikh (2020) Fig 1 explicitly cites Census,</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>- USA Trade Online auth-required path: not used; we stick to the</t>
+          <t xml:space="preserve">  not US Bureau of Economic Analysis (BEA) International Transactions. Census</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t xml:space="preserve">  public HTML/text pages.</t>
+          <t xml:space="preserve">  FT900 is the published recipe.</t>
         </is>
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>- Methodology continuity: paper-window 2002-2017 values were Census-basis</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>## 6. Conceptual continuity vs adjacent concepts</t>
+          <t xml:space="preserve">  monthly aggregates; 2018-2024 extension uses the *same* FT900 release</t>
         </is>
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (same agency, same exhibit numbers).</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>The extension proxy `Census FT900 Exhibit 1 (world) + c5700 (China)` measures</t>
+          <t>- Disambiguation: Census-basis (Total Exports Value − Customs Import Value)</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>`US merchandise (goods) trade balance, Census basis` rather than</t>
+          <t xml:space="preserve">  differs from BoP-basis (BEA International Transactions Accounts (ITA)</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>`US current account` or `BoP-basis goods balance` because:</t>
+          <t xml:space="preserve">  Table 4.1, which makes balance-of-payments coverage and timing</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>- Source agency choice: Weber &amp; Shaikh (2020) Fig 1 explicitly cites Census,</t>
+          <t xml:space="preserve">  adjustments), and from current-account (which adds</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t xml:space="preserve">  not BEA International Transactions. Census FT900 is the published recipe.</t>
+          <t xml:space="preserve">  services, primary income, and secondary income).</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>- Methodology continuity: paper-window 2002-2017 values were Census-basis</t>
-        </is>
-      </c>
+      <c r="A177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t xml:space="preserve">  monthly aggregates; 2018-2024 extension uses the *same* FT900 release</t>
+          <t>The book's original concept (paper p. 432, Fig 1 footnote) was: "Total Exports</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t xml:space="preserve">  (same agency, same exhibit numbers).</t>
+          <t>Value minus Customs Import Value". The modern series preserves Census-basis</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>- Disambiguation: Census-basis (Total Exports Value − Customs Import Value)</t>
+          <t>goods coverage and the bilateral US-China decomposition while permitting a</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t xml:space="preserve">  differs from BoP-basis (BEA ITA Table 4.1, which makes balance-of-payments</t>
+          <t>small post-2018 Section-301-tariff valuation effect (customs values now</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t xml:space="preserve">  coverage and timing adjustments), and from current-account (which adds</t>
+          <t>include tariff-inclusive imports for some Harmonized Tariff Schedule (HTS)</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t xml:space="preserve">  services, primary income, and secondary income).</t>
+          <t>lines). This is not a proxy substitution: the loader pulls from *exactly* the</t>
         </is>
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr"/>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>source the paper cites (US Census FT900) — no change of agency, no change of</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>The book's original concept (paper p. 432, Fig 1 footnote) was: "Total Exports</t>
+          <t>concept.</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Value minus Customs Import Value". The modern series preserves Census-basis</t>
-        </is>
-      </c>
+      <c r="A186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>goods coverage and the bilateral US-China decomposition while permitting a</t>
+          <t>## 7. Method note: Census-basis vs BoP-basis</t>
         </is>
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>small post-2018 Section-301-tariff valuation effect (customs values now</t>
-        </is>
-      </c>
+      <c r="A188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>include tariff-inclusive imports for some HTS lines). This is NOT a proxy</t>
+          <t>We reproduce Census basis to match paper recipe; BEA International</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>substitution forbidden by the No-Proxy rule because the loader pulls from</t>
+          <t>Transactions Table 4.1 BoP-basis goods balance is concept-adjacent but</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
-        <is>
-          <t>*exactly* the source the paper cites (US Census FT900) — no agency</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>substitution, no concept substitution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>## 7. Method note: Census-basis vs BoP-basis</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr"/>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>We reproduce Census basis to match paper recipe; BEA International</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>Transactions Table 4.1 BoP-basis goods balance is concept-adjacent but</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
         <is>
           <t>methodologically distinct and is NOT used.</t>
         </is>
@@ -3549,7 +3504,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-06-11T04:43:02.195531+00:00</t>
+          <t>2026-07-02T06:29:17.412966+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/XS2301_extenbook.xlsx
+++ b/extenbooks/XS2301_extenbook.xlsx
@@ -621,8 +621,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="57" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
   </cols>
@@ -657,7 +657,7 @@
         <v>2002</v>
       </c>
       <c r="B4" t="n">
-        <v>-103.065</v>
+        <v>-103.0649</v>
       </c>
       <c r="C4" t="n">
         <v>-468.262</v>
@@ -668,7 +668,7 @@
         <v>2003</v>
       </c>
       <c r="B5" t="n">
-        <v>-124.068</v>
+        <v>-124.0682</v>
       </c>
       <c r="C5" t="n">
         <v>-532.35</v>
@@ -679,10 +679,10 @@
         <v>2004</v>
       </c>
       <c r="B6" t="n">
-        <v>-162.254</v>
+        <v>-162.2543</v>
       </c>
       <c r="C6" t="n">
-        <v>-654.828</v>
+        <v>-654.8285</v>
       </c>
     </row>
     <row r="7">
@@ -690,10 +690,10 @@
         <v>2005</v>
       </c>
       <c r="B7" t="n">
-        <v>-202.278</v>
+        <v>-202.2781</v>
       </c>
       <c r="C7" t="n">
-        <v>-772.374</v>
+        <v>-772.3742</v>
       </c>
     </row>
     <row r="8">
@@ -701,7 +701,7 @@
         <v>2006</v>
       </c>
       <c r="B8" t="n">
-        <v>-234.101</v>
+        <v>-234.1013</v>
       </c>
       <c r="C8" t="n">
         <v>-827.97</v>
@@ -723,7 +723,7 @@
         <v>2008</v>
       </c>
       <c r="B10" t="n">
-        <v>-268.04</v>
+        <v>-268.0398</v>
       </c>
       <c r="C10" t="n">
         <v>-816.2</v>
@@ -734,7 +734,7 @@
         <v>2009</v>
       </c>
       <c r="B11" t="n">
-        <v>-226.877</v>
+        <v>-226.8772</v>
       </c>
       <c r="C11" t="n">
         <v>-503.583</v>
@@ -745,7 +745,7 @@
         <v>2010</v>
       </c>
       <c r="B12" t="n">
-        <v>-273.042</v>
+        <v>-273.0416</v>
       </c>
       <c r="C12" t="n">
         <v>-635.365</v>
@@ -756,7 +756,7 @@
         <v>2011</v>
       </c>
       <c r="B13" t="n">
-        <v>-295.25</v>
+        <v>-295.2497</v>
       </c>
       <c r="C13" t="n">
         <v>-725.447</v>
@@ -767,10 +767,10 @@
         <v>2012</v>
       </c>
       <c r="B14" t="n">
-        <v>-315.103</v>
+        <v>-315.1025</v>
       </c>
       <c r="C14" t="n">
-        <v>-730.446</v>
+        <v>-730.4463000000001</v>
       </c>
     </row>
     <row r="15">
@@ -778,10 +778,10 @@
         <v>2013</v>
       </c>
       <c r="B15" t="n">
-        <v>-318.684</v>
+        <v>-318.6838</v>
       </c>
       <c r="C15" t="n">
-        <v>-689.47</v>
+        <v>-689.4699000000001</v>
       </c>
     </row>
     <row r="16">
@@ -789,10 +789,10 @@
         <v>2014</v>
       </c>
       <c r="B16" t="n">
-        <v>-344.818</v>
+        <v>-344.8177</v>
       </c>
       <c r="C16" t="n">
-        <v>-734.482</v>
+        <v>-734.4823</v>
       </c>
     </row>
     <row r="17">
@@ -800,7 +800,7 @@
         <v>2015</v>
       </c>
       <c r="B17" t="n">
-        <v>-367.328</v>
+        <v>-367.3283</v>
       </c>
       <c r="C17" t="n">
         <v>-745.4829999999999</v>
@@ -811,7 +811,7 @@
         <v>2016</v>
       </c>
       <c r="B18" t="n">
-        <v>-346.825</v>
+        <v>-346.8252</v>
       </c>
       <c r="C18" t="n">
         <v>-735.326</v>
@@ -822,10 +822,10 @@
         <v>2017</v>
       </c>
       <c r="B19" t="n">
-        <v>-375.168</v>
+        <v>-375.1679</v>
       </c>
       <c r="C19" t="n">
-        <v>-792.396</v>
+        <v>-792.3959</v>
       </c>
     </row>
     <row r="20">
@@ -833,10 +833,10 @@
         <v>2018</v>
       </c>
       <c r="B20" t="n">
-        <v>-418.233</v>
+        <v>-418.2329</v>
       </c>
       <c r="C20" t="n">
-        <v>-870.3579999999999</v>
+        <v>-870.3584000000001</v>
       </c>
     </row>
     <row r="21">
@@ -844,10 +844,10 @@
         <v>2019</v>
       </c>
       <c r="B21" t="n">
-        <v>-342.63</v>
+        <v>-342.6295</v>
       </c>
       <c r="C21" t="n">
-        <v>-845.759</v>
+        <v>-845.7592</v>
       </c>
     </row>
     <row r="22">
@@ -855,10 +855,10 @@
         <v>2020</v>
       </c>
       <c r="B22" t="n">
-        <v>-307.966</v>
+        <v>-307.9665</v>
       </c>
       <c r="C22" t="n">
-        <v>-901.482</v>
+        <v>-901.4818</v>
       </c>
     </row>
     <row r="23">
@@ -866,10 +866,10 @@
         <v>2021</v>
       </c>
       <c r="B23" t="n">
-        <v>-352.807</v>
+        <v>-352.8069</v>
       </c>
       <c r="C23" t="n">
-        <v>-1070.772</v>
+        <v>-1070.7718</v>
       </c>
     </row>
     <row r="24">
@@ -877,10 +877,10 @@
         <v>2022</v>
       </c>
       <c r="B24" t="n">
-        <v>-382.281</v>
+        <v>-382.2813</v>
       </c>
       <c r="C24" t="n">
-        <v>-1167.085</v>
+        <v>-1167.0849</v>
       </c>
     </row>
     <row r="25">
@@ -888,7 +888,7 @@
         <v>2023</v>
       </c>
       <c r="B25" t="n">
-        <v>-279.608</v>
+        <v>-279.6078</v>
       </c>
       <c r="C25" t="n">
         <v>-1054.613</v>
@@ -899,10 +899,10 @@
         <v>2024</v>
       </c>
       <c r="B26" t="n">
-        <v>-297.048</v>
+        <v>-297.0477</v>
       </c>
       <c r="C26" t="n">
-        <v>-1200.869</v>
+        <v>-1200.8688</v>
       </c>
     </row>
     <row r="27"/>
@@ -947,7 +947,7 @@
         <v>2002</v>
       </c>
       <c r="B32" t="n">
-        <v>-103.065</v>
+        <v>-103.0649</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>2003</v>
       </c>
       <c r="B33" t="n">
-        <v>-124.068</v>
+        <v>-124.0682</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>2004</v>
       </c>
       <c r="B34" t="n">
-        <v>-162.254</v>
+        <v>-162.2543</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1016,7 +1016,7 @@
         <v>2005</v>
       </c>
       <c r="B35" t="n">
-        <v>-202.278</v>
+        <v>-202.2781</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>2006</v>
       </c>
       <c r="B36" t="n">
-        <v>-234.101</v>
+        <v>-234.1013</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1085,7 +1085,7 @@
         <v>2008</v>
       </c>
       <c r="B38" t="n">
-        <v>-268.04</v>
+        <v>-268.0398</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>2009</v>
       </c>
       <c r="B39" t="n">
-        <v>-226.877</v>
+        <v>-226.8772</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>2010</v>
       </c>
       <c r="B40" t="n">
-        <v>-273.042</v>
+        <v>-273.0416</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>2011</v>
       </c>
       <c r="B41" t="n">
-        <v>-295.25</v>
+        <v>-295.2497</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1177,7 +1177,7 @@
         <v>2012</v>
       </c>
       <c r="B42" t="n">
-        <v>-315.103</v>
+        <v>-315.1025</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
         <v>2013</v>
       </c>
       <c r="B43" t="n">
-        <v>-318.684</v>
+        <v>-318.6838</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>2014</v>
       </c>
       <c r="B44" t="n">
-        <v>-344.818</v>
+        <v>-344.8177</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>2015</v>
       </c>
       <c r="B45" t="n">
-        <v>-367.328</v>
+        <v>-367.3283</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         <v>2016</v>
       </c>
       <c r="B46" t="n">
-        <v>-346.825</v>
+        <v>-346.8252</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -1292,7 +1292,7 @@
         <v>2017</v>
       </c>
       <c r="B47" t="n">
-        <v>-375.168</v>
+        <v>-375.1679</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
         <v>2018</v>
       </c>
       <c r="B48" t="n">
-        <v>-418.233</v>
+        <v>-418.2329</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>2019</v>
       </c>
       <c r="B49" t="n">
-        <v>-342.63</v>
+        <v>-342.6295</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
         <v>2020</v>
       </c>
       <c r="B50" t="n">
-        <v>-307.966</v>
+        <v>-307.9665</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -1384,7 +1384,7 @@
         <v>2021</v>
       </c>
       <c r="B51" t="n">
-        <v>-352.807</v>
+        <v>-352.8069</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>2022</v>
       </c>
       <c r="B52" t="n">
-        <v>-382.281</v>
+        <v>-382.2813</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -1430,7 +1430,7 @@
         <v>2023</v>
       </c>
       <c r="B53" t="n">
-        <v>-279.608</v>
+        <v>-279.6078</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>2024</v>
       </c>
       <c r="B54" t="n">
-        <v>-297.048</v>
+        <v>-297.0477</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -1522,7 +1522,7 @@
         <v>2004</v>
       </c>
       <c r="B57" t="n">
-        <v>-654.828</v>
+        <v>-654.8285</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>2005</v>
       </c>
       <c r="B58" t="n">
-        <v>-772.374</v>
+        <v>-772.3742</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
         <v>2012</v>
       </c>
       <c r="B65" t="n">
-        <v>-730.446</v>
+        <v>-730.4463000000001</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>2013</v>
       </c>
       <c r="B66" t="n">
-        <v>-689.47</v>
+        <v>-689.4699000000001</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
         <v>2014</v>
       </c>
       <c r="B67" t="n">
-        <v>-734.482</v>
+        <v>-734.4823</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -1821,7 +1821,7 @@
         <v>2017</v>
       </c>
       <c r="B70" t="n">
-        <v>-792.396</v>
+        <v>-792.3959</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>2018</v>
       </c>
       <c r="B71" t="n">
-        <v>-870.3579999999999</v>
+        <v>-870.3584000000001</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>2019</v>
       </c>
       <c r="B72" t="n">
-        <v>-845.759</v>
+        <v>-845.7592</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>2020</v>
       </c>
       <c r="B73" t="n">
-        <v>-901.482</v>
+        <v>-901.4818</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -1913,7 +1913,7 @@
         <v>2021</v>
       </c>
       <c r="B74" t="n">
-        <v>-1070.772</v>
+        <v>-1070.7718</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -1936,7 +1936,7 @@
         <v>2022</v>
       </c>
       <c r="B75" t="n">
-        <v>-1167.085</v>
+        <v>-1167.0849</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -1982,7 +1982,7 @@
         <v>2024</v>
       </c>
       <c r="B77" t="n">
-        <v>-1200.869</v>
+        <v>-1200.8688</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>The extension proxy `Census FT900 Exhibit 1 (world) + c5700 (China)` measures</t>
+          <t>The extension proxy `Census FT900 c0004 (world) + c5700 (China)` measures</t>
         </is>
       </c>
     </row>
@@ -3178,10 +3178,10 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
-    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="57" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="38" customWidth="1" min="7" max="7"/>
-    <col width="51" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
@@ -3287,12 +3287,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CENSUS_FT900_EXH1</t>
+          <t>CENSUS_FT900_C0004</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US Census FT900 Exhibit 1 — US Total Goods Trade</t>
+          <t>US Census FT900 Trade in Goods with the World / all countries (per-country page c0004)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -3302,7 +3302,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.census.gov/foreign-trade/statistics/historical/exh1.txt</t>
+          <t>https://www.census.gov/foreign-trade/balance/c0004.html</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Public domain (US Federal Government, 17 USC 105)</t>
+          <t>Public domain</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-07-02T06:29:17.412966+00:00</t>
+          <t>2026-07-11T03:44:27.759924+00:00</t>
         </is>
       </c>
     </row>
@@ -3519,11 +3519,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3546,6 +3546,162 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CENSUS_FT900_C0004</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>direct</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>study_complete</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>study_replication</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Truncation repaired this pass. The loader's fragile Census scrape mis-keyed the annual figure off a non-existent column header and silently fell back to five Fig-1 anchor points, truncating at 2018 while the DPR falsely claimed continuous coverage to 2024. Loader rebuilt on the Census FT900 country balance pages (c0004 World, c5700 China), reading the published TOTAL {YYYY} rows directly. Now genuinely continuous 2002-2024, 23 real annual observations per partner, all live Census data, zero fabrication. V03 validator PASS (4/4 Fig-1 anchors matched, max 2.17% error). DPR + EPR corrected.", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS2301_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/XS2301_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Decision 0001: ES placeholder. Phase 3 subagent must read the paper PDF, identify empirical figures, and either populate this placeholder as a single series OR expand to N series ES{group}01..ES{group}NN. | Rescoped per decision 0006 to Fig 1 only; XS2302-XS2305 hold the other 4 figures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>billion_usd</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
